--- a/data/trans_orig/P1806_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1806_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 12 meses han visitado un podólogo en 2023</t>
+          <t>Población según si en los últimos 12 meses han visitado un podólogo en 2023 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8467</t>
+          <t>8347</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23036</t>
+          <t>23546</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43566</t>
+          <t>43292</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>65080</t>
+          <t>63607</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55597</t>
+          <t>55084</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80204</t>
+          <t>79488</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>491902</t>
+          <t>491392</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>506471</t>
+          <t>506591</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>689862</t>
+          <t>691335</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>711376</t>
+          <t>711650</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1189677</t>
+          <t>1190393</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1214284</t>
+          <t>1214797</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27619</t>
+          <t>26763</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59916</t>
+          <t>59730</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61003</t>
+          <t>59479</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105865</t>
+          <t>102533</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>99251</t>
+          <t>99087</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>153324</t>
+          <t>150067</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2230411</t>
+          <t>2230597</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2262708</t>
+          <t>2263564</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2131280</t>
+          <t>2134612</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2176142</t>
+          <t>2177666</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4374148</t>
+          <t>4377405</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4428221</t>
+          <t>4428385</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14071</t>
+          <t>14095</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33967</t>
+          <t>32951</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34608</t>
+          <t>34331</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56676</t>
+          <t>56919</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>52342</t>
+          <t>54255</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81404</t>
+          <t>81187</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>612656</t>
+          <t>613672</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>632552</t>
+          <t>632528</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>603787</t>
+          <t>603544</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>625855</t>
+          <t>626132</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1225682</t>
+          <t>1225899</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1254744</t>
+          <t>1252831</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,85%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57877</t>
+          <t>59732</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>99634</t>
+          <t>101063</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>147456</t>
+          <t>147119</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>205176</t>
+          <t>206093</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>220316</t>
+          <t>223394</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>295110</t>
+          <t>293016</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3352255</t>
+          <t>3350826</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3394012</t>
+          <t>3392157</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3447374</t>
+          <t>3446457</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3505094</t>
+          <t>3505431</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6809329</t>
+          <t>6811423</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6884123</t>
+          <t>6881045</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,86%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1806_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1806_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>13822</t>
+          <t>14376</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8347</t>
+          <t>9326</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23546</t>
+          <t>24005</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>52942</t>
+          <t>56746</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43292</t>
+          <t>46950</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63607</t>
+          <t>68835</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>66764</t>
+          <t>71122</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55084</t>
+          <t>59055</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79488</t>
+          <t>84916</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>501116</t>
+          <t>564153</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>491392</t>
+          <t>554524</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>506591</t>
+          <t>569203</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>702000</t>
+          <t>764696</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>691335</t>
+          <t>752607</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>711650</t>
+          <t>774492</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1203117</t>
+          <t>1328849</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1190393</t>
+          <t>1315055</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1214797</t>
+          <t>1340916</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,78%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>754942</t>
+          <t>821442</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>754942</t>
+          <t>821442</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>754942</t>
+          <t>821442</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1269881</t>
+          <t>1399971</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1269881</t>
+          <t>1399971</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1269881</t>
+          <t>1399971</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>43167</t>
+          <t>44298</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26763</t>
+          <t>31544</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59730</t>
+          <t>61333</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>81982</t>
+          <t>88551</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59479</t>
+          <t>73392</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>102533</t>
+          <t>106961</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>125149</t>
+          <t>132849</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>99087</t>
+          <t>112541</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>150067</t>
+          <t>156085</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2247160</t>
+          <t>2186268</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2230597</t>
+          <t>2169233</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2263564</t>
+          <t>2199022</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2155163</t>
+          <t>2082156</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2134612</t>
+          <t>2063746</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2177666</t>
+          <t>2097315</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4402323</t>
+          <t>4268425</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4377405</t>
+          <t>4245189</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4428385</t>
+          <t>4288733</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,44%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,67 +1411,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>22018</t>
+          <t>22600</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14095</t>
+          <t>15282</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32951</t>
+          <t>36674</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>5,15%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>48172</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>37498</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>60224</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>6,56%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>5,1%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>43882</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>34331</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>56919</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>6,64%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>5,2%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>65899</t>
+          <t>70772</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54255</t>
+          <t>55830</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81187</t>
+          <t>86873</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -1524,69 +1524,69 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>624605</t>
+          <t>688987</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>613672</t>
+          <t>674913</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>632528</t>
+          <t>696305</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>94,85%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,85%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>686705</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>674653</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>697379</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>93,44%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>91,8%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>94,9%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,82%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>616581</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>603544</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>626132</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>93,36%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>91,38%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>94,8%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>1589</t>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1241187</t>
+          <t>1375692</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1225899</t>
+          <t>1359591</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1252831</t>
+          <t>1390634</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,14%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>79007</t>
+          <t>81274</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59732</t>
+          <t>65227</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>101063</t>
+          <t>101243</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>178806</t>
+          <t>193469</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>147119</t>
+          <t>172896</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>206093</t>
+          <t>217853</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>257813</t>
+          <t>274743</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>223394</t>
+          <t>247848</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>293016</t>
+          <t>304607</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3372882</t>
+          <t>3439409</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3350826</t>
+          <t>3419440</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3392157</t>
+          <t>3455456</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3473744</t>
+          <t>3533557</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3446457</t>
+          <t>3509173</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3505431</t>
+          <t>3554130</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6846626</t>
+          <t>6972966</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6811423</t>
+          <t>6943102</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6881045</t>
+          <t>6999861</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3652550</t>
+          <t>3727026</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3652550</t>
+          <t>3727026</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3652550</t>
+          <t>3727026</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7104439</t>
+          <t>7247709</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7104439</t>
+          <t>7247709</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7104439</t>
+          <t>7247709</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
